--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/33.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/33.xlsx
@@ -426,13 +426,13 @@
         <v>-7.765594252281317</v>
       </c>
       <c r="E2">
-        <v>-11.66905994067872</v>
+        <v>-21.66138237619978</v>
       </c>
       <c r="F2">
-        <v>-3.354488027129953</v>
+        <v>-5.252710154727882</v>
       </c>
       <c r="G2">
-        <v>-6.937049234083473</v>
+        <v>-13.58314381540939</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-8.082125281042099</v>
       </c>
       <c r="E3">
-        <v>-13.38076877389003</v>
+        <v>-22.1218376132997</v>
       </c>
       <c r="F3">
-        <v>-3.239251352624306</v>
+        <v>-5.537049750841021</v>
       </c>
       <c r="G3">
-        <v>-7.486329004356077</v>
+        <v>-13.01192907901189</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-8.402910009692674</v>
       </c>
       <c r="E4">
-        <v>-13.02375294007331</v>
+        <v>-23.22949782710187</v>
       </c>
       <c r="F4">
-        <v>-3.124293009565999</v>
+        <v>-4.840086269147601</v>
       </c>
       <c r="G4">
-        <v>-7.466966515933794</v>
+        <v>-13.4439576780793</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-8.670353662899412</v>
       </c>
       <c r="E5">
-        <v>-12.99544997752537</v>
+        <v>-23.3808937701263</v>
       </c>
       <c r="F5">
-        <v>-2.981255496654997</v>
+        <v>-4.892565000849755</v>
       </c>
       <c r="G5">
-        <v>-6.868196080880084</v>
+        <v>-13.69679220534231</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-8.883148009040216</v>
       </c>
       <c r="E6">
-        <v>-14.2389961108757</v>
+        <v>-23.0064704822241</v>
       </c>
       <c r="F6">
-        <v>-3.04216700851765</v>
+        <v>-5.1285569334985</v>
       </c>
       <c r="G6">
-        <v>-7.20953171604444</v>
+        <v>-13.25272152315175</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-9.035964377050073</v>
       </c>
       <c r="E7">
-        <v>-14.96920348766453</v>
+        <v>-25.55064869226545</v>
       </c>
       <c r="F7">
-        <v>-2.997203225893693</v>
+        <v>-4.303745711959214</v>
       </c>
       <c r="G7">
-        <v>-6.541858909463951</v>
+        <v>-13.75832495324658</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-9.132447334443922</v>
       </c>
       <c r="E8">
-        <v>-15.43060517583205</v>
+        <v>-26.08465993267196</v>
       </c>
       <c r="F8">
-        <v>-2.694194713623662</v>
+        <v>-4.717712381099433</v>
       </c>
       <c r="G8">
-        <v>-7.275129897460858</v>
+        <v>-14.01706239809504</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-9.176538738440328</v>
       </c>
       <c r="E9">
-        <v>-15.92660440541818</v>
+        <v>-27.55040470015664</v>
       </c>
       <c r="F9">
-        <v>-2.849261777958118</v>
+        <v>-4.941347557200618</v>
       </c>
       <c r="G9">
-        <v>-6.748073840810373</v>
+        <v>-13.10257610581311</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-9.17154422282808</v>
       </c>
       <c r="E10">
-        <v>-16.86937835212706</v>
+        <v>-26.23241951106823</v>
       </c>
       <c r="F10">
-        <v>-2.827849308963154</v>
+        <v>-4.953710940687401</v>
       </c>
       <c r="G10">
-        <v>-6.412952839279606</v>
+        <v>-12.53627663931167</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-9.116284061700393</v>
       </c>
       <c r="E11">
-        <v>-17.25568888429939</v>
+        <v>-27.84959192089541</v>
       </c>
       <c r="F11">
-        <v>-2.524955939762112</v>
+        <v>-4.116315161564783</v>
       </c>
       <c r="G11">
-        <v>-6.290927490705416</v>
+        <v>-13.08041145417907</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-9.014053580357949</v>
       </c>
       <c r="E12">
-        <v>-17.55428287494315</v>
+        <v>-27.81686463924198</v>
       </c>
       <c r="F12">
-        <v>-2.388461700965823</v>
+        <v>-4.524994361572933</v>
       </c>
       <c r="G12">
-        <v>-4.501487063489765</v>
+        <v>-11.95194686034108</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-8.866267977656904</v>
       </c>
       <c r="E13">
-        <v>-17.62774378029558</v>
+        <v>-26.60727300400116</v>
       </c>
       <c r="F13">
-        <v>-2.466355572953269</v>
+        <v>-4.141343454272968</v>
       </c>
       <c r="G13">
-        <v>-4.740770145712271</v>
+        <v>-10.67425887242266</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-8.686992611274114</v>
       </c>
       <c r="E14">
-        <v>-20.01207591481418</v>
+        <v>-29.16917566130853</v>
       </c>
       <c r="F14">
-        <v>-2.355639299364698</v>
+        <v>-4.106072398629167</v>
       </c>
       <c r="G14">
-        <v>-3.795903023011451</v>
+        <v>-10.90470562498558</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-8.487302922459364</v>
       </c>
       <c r="E15">
-        <v>-19.6720871432663</v>
+        <v>-29.14671895870449</v>
       </c>
       <c r="F15">
-        <v>-2.043153435639238</v>
+        <v>-3.968000119930545</v>
       </c>
       <c r="G15">
-        <v>-3.989514782348047</v>
+        <v>-10.27975760433062</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-8.284448319863509</v>
       </c>
       <c r="E16">
-        <v>-21.19762135307426</v>
+        <v>-29.45388535064477</v>
       </c>
       <c r="F16">
-        <v>-1.499684776949761</v>
+        <v>-4.245644850694259</v>
       </c>
       <c r="G16">
-        <v>-3.909528444393462</v>
+        <v>-9.31535408846487</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-8.086062210844144</v>
       </c>
       <c r="E17">
-        <v>-21.24887009341907</v>
+        <v>-29.55321063529201</v>
       </c>
       <c r="F17">
-        <v>-1.746189520307435</v>
+        <v>-3.600354927587472</v>
       </c>
       <c r="G17">
-        <v>-2.974655922562712</v>
+        <v>-9.882897137937343</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-7.897582207042139</v>
       </c>
       <c r="E18">
-        <v>-22.02659021949637</v>
+        <v>-31.42198053251134</v>
       </c>
       <c r="F18">
-        <v>-1.249308244351402</v>
+        <v>-2.866915944046581</v>
       </c>
       <c r="G18">
-        <v>-2.956320456488535</v>
+        <v>-9.003510072676804</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-7.713939741037631</v>
       </c>
       <c r="E19">
-        <v>-23.35193417884725</v>
+        <v>-32.72468665029788</v>
       </c>
       <c r="F19">
-        <v>-1.240276554558679</v>
+        <v>-3.435615017090526</v>
       </c>
       <c r="G19">
-        <v>-1.15921837693158</v>
+        <v>-7.977114437888461</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-7.52999743921467</v>
       </c>
       <c r="E20">
-        <v>-24.39552101391488</v>
+        <v>-32.04328490212671</v>
       </c>
       <c r="F20">
-        <v>-0.5555505445068157</v>
+        <v>-3.506992951087551</v>
       </c>
       <c r="G20">
-        <v>-2.33778394276073</v>
+        <v>-10.03451582375616</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-7.337477716778585</v>
       </c>
       <c r="E21">
-        <v>-23.75223769570329</v>
+        <v>-31.98880056710343</v>
       </c>
       <c r="F21">
-        <v>-0.4278063505862985</v>
+        <v>-2.822874962709343</v>
       </c>
       <c r="G21">
-        <v>-2.266948931735438</v>
+        <v>-8.647504095920171</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-7.134280324472278</v>
       </c>
       <c r="E22">
-        <v>-24.53431421377597</v>
+        <v>-30.48990284140859</v>
       </c>
       <c r="F22">
-        <v>-0.1703613589398513</v>
+        <v>-3.098977273369043</v>
       </c>
       <c r="G22">
-        <v>-2.466611263627649</v>
+        <v>-8.699308021900684</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-6.923049032348557</v>
       </c>
       <c r="E23">
-        <v>-25.49440051661617</v>
+        <v>-33.30381281300581</v>
       </c>
       <c r="F23">
-        <v>-0.1175007498650064</v>
+        <v>-2.887688085039182</v>
       </c>
       <c r="G23">
-        <v>-2.158225655363237</v>
+        <v>-9.346358350980063</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-6.71291888515819</v>
       </c>
       <c r="E24">
-        <v>-25.68480020626867</v>
+        <v>-34.18540028316004</v>
       </c>
       <c r="F24">
-        <v>0.1704670954723941</v>
+        <v>-2.278950701948326</v>
       </c>
       <c r="G24">
-        <v>-2.2820655194598</v>
+        <v>-8.683692688499287</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-6.518536125659788</v>
       </c>
       <c r="E25">
-        <v>-26.04286211758116</v>
+        <v>-32.61788711930098</v>
       </c>
       <c r="F25">
-        <v>0.3912311501554763</v>
+        <v>-2.958752896157948</v>
       </c>
       <c r="G25">
-        <v>-2.95345266884558</v>
+        <v>-7.671622867039479</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-6.350645926096675</v>
       </c>
       <c r="E26">
-        <v>-25.43610547071543</v>
+        <v>-34.28111410978616</v>
       </c>
       <c r="F26">
-        <v>0.6300991744267418</v>
+        <v>-2.391752804657146</v>
       </c>
       <c r="G26">
-        <v>-2.294311038319647</v>
+        <v>-8.036970481575851</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-6.222595344832599</v>
       </c>
       <c r="E27">
-        <v>-26.34214443627409</v>
+        <v>-32.93018200805495</v>
       </c>
       <c r="F27">
-        <v>0.6479753429791552</v>
+        <v>-1.76278503285512</v>
       </c>
       <c r="G27">
-        <v>-2.815795580762196</v>
+        <v>-8.934295985101876</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-6.136305124552015</v>
       </c>
       <c r="E28">
-        <v>-25.25595371774229</v>
+        <v>-32.47871352762325</v>
       </c>
       <c r="F28">
-        <v>0.568259891072953</v>
+        <v>-1.53788493972986</v>
       </c>
       <c r="G28">
-        <v>-3.246682314726917</v>
+        <v>-9.545121628164985</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-6.096230967946625</v>
       </c>
       <c r="E29">
-        <v>-25.71422170189651</v>
+        <v>-32.52260349770559</v>
       </c>
       <c r="F29">
-        <v>0.5950550914513087</v>
+        <v>-2.748903410374152</v>
       </c>
       <c r="G29">
-        <v>-3.323282432032153</v>
+        <v>-10.59368519580894</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-6.095366556708724</v>
       </c>
       <c r="E30">
-        <v>-24.90393279075603</v>
+        <v>-34.45977825904779</v>
       </c>
       <c r="F30">
-        <v>0.7651205759808528</v>
+        <v>-2.572533221541901</v>
       </c>
       <c r="G30">
-        <v>-3.261989213301726</v>
+        <v>-9.85113163202036</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-6.12605246423687</v>
       </c>
       <c r="E31">
-        <v>-25.29474462609199</v>
+        <v>-33.25072324797688</v>
       </c>
       <c r="F31">
-        <v>0.70765341577904</v>
+        <v>-1.855731168918836</v>
       </c>
       <c r="G31">
-        <v>-3.24388343273671</v>
+        <v>-8.607965376128861</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-6.17126913849348</v>
       </c>
       <c r="E32">
-        <v>-25.01758843140054</v>
+        <v>-32.63341072819927</v>
       </c>
       <c r="F32">
-        <v>0.2881317148356471</v>
+        <v>-1.977527684887253</v>
       </c>
       <c r="G32">
-        <v>-3.225068908314854</v>
+        <v>-9.557751049947289</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-6.215845548482417</v>
       </c>
       <c r="E33">
-        <v>-25.10988326015087</v>
+        <v>-32.51031095501177</v>
       </c>
       <c r="F33">
-        <v>0.3861888777746358</v>
+        <v>-2.142334693143825</v>
       </c>
       <c r="G33">
-        <v>-3.726226283196643</v>
+        <v>-9.623007984321525</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-6.241486028626788</v>
       </c>
       <c r="E34">
-        <v>-23.70854245000328</v>
+        <v>-30.5352509801214</v>
       </c>
       <c r="F34">
-        <v>0.492333391667156</v>
+        <v>-1.488311292509324</v>
       </c>
       <c r="G34">
-        <v>-3.442945301083543</v>
+        <v>-9.24083754684988</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.233579656202054</v>
       </c>
       <c r="E35">
-        <v>-23.59132742878873</v>
+        <v>-31.3555342333968</v>
       </c>
       <c r="F35">
-        <v>0.6246493452837238</v>
+        <v>-2.918909252450695</v>
       </c>
       <c r="G35">
-        <v>-3.572917768274707</v>
+        <v>-9.646947776819234</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.178596377730878</v>
       </c>
       <c r="E36">
-        <v>-22.80044755724514</v>
+        <v>-31.42194204048228</v>
       </c>
       <c r="F36">
-        <v>0.4895633310721945</v>
+        <v>-2.886860546003785</v>
       </c>
       <c r="G36">
-        <v>-3.065148731950638</v>
+        <v>-8.61760888629207</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-6.069797705314676</v>
       </c>
       <c r="E37">
-        <v>-23.60991681459022</v>
+        <v>-33.28787258449881</v>
       </c>
       <c r="F37">
-        <v>0.4529287826833863</v>
+        <v>-2.685569752225713</v>
       </c>
       <c r="G37">
-        <v>-3.373760744502651</v>
+        <v>-10.7831330849866</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.907580533492673</v>
       </c>
       <c r="E38">
-        <v>-22.50248755296245</v>
+        <v>-29.75727046678865</v>
       </c>
       <c r="F38">
-        <v>0.5664896699331705</v>
+        <v>-3.2750235705468</v>
       </c>
       <c r="G38">
-        <v>-3.279094221291111</v>
+        <v>-10.27426155821855</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-5.697392175385927</v>
       </c>
       <c r="E39">
-        <v>-21.62335677995738</v>
+        <v>-30.53373167709182</v>
       </c>
       <c r="F39">
-        <v>-0.07014961238618109</v>
+        <v>-2.931121873070168</v>
       </c>
       <c r="G39">
-        <v>-3.336295756736911</v>
+        <v>-9.534690624827512</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-5.45223208184006</v>
       </c>
       <c r="E40">
-        <v>-21.60120348511185</v>
+        <v>-29.09037568510106</v>
       </c>
       <c r="F40">
-        <v>0.4935858831801889</v>
+        <v>-2.234640501205177</v>
       </c>
       <c r="G40">
-        <v>-2.073917948614865</v>
+        <v>-9.706918663261204</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-5.182853876146584</v>
       </c>
       <c r="E41">
-        <v>-20.84116252156049</v>
+        <v>-28.27848822263588</v>
       </c>
       <c r="F41">
-        <v>-0.04087593673864936</v>
+        <v>-2.470530544663379</v>
       </c>
       <c r="G41">
-        <v>-2.292752458078911</v>
+        <v>-9.957774613923872</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.905993296712505</v>
       </c>
       <c r="E42">
-        <v>-20.59882123504001</v>
+        <v>-28.07036408571735</v>
       </c>
       <c r="F42">
-        <v>0.3648534469481317</v>
+        <v>-1.898271148522202</v>
       </c>
       <c r="G42">
-        <v>-2.377404693091025</v>
+        <v>-8.839547431351351</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.631870311848115</v>
       </c>
       <c r="E43">
-        <v>-19.50944247080681</v>
+        <v>-28.4974127700627</v>
       </c>
       <c r="F43">
-        <v>0.01112234186988121</v>
+        <v>-2.930742480799686</v>
       </c>
       <c r="G43">
-        <v>-1.675403746555626</v>
+        <v>-9.690958801596066</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.375246155622575</v>
       </c>
       <c r="E44">
-        <v>-19.64366191192016</v>
+        <v>-27.53105905919588</v>
       </c>
       <c r="F44">
-        <v>-0.1936931552071021</v>
+        <v>-2.755404437751323</v>
       </c>
       <c r="G44">
-        <v>-1.665894766476355</v>
+        <v>-9.322428402147033</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.144467862303681</v>
       </c>
       <c r="E45">
-        <v>-19.2224504305707</v>
+        <v>-28.37433790348223</v>
       </c>
       <c r="F45">
-        <v>-0.01866574993478901</v>
+        <v>-2.61447926171746</v>
       </c>
       <c r="G45">
-        <v>-2.0341167310988</v>
+        <v>-11.14776867444457</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.950295709544676</v>
       </c>
       <c r="E46">
-        <v>-17.97074398705856</v>
+        <v>-28.10632922628627</v>
       </c>
       <c r="F46">
-        <v>0.3463916226419391</v>
+        <v>-2.548347378482364</v>
       </c>
       <c r="G46">
-        <v>-1.457881725715357</v>
+        <v>-9.229543582242272</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.798222881264711</v>
       </c>
       <c r="E47">
-        <v>-17.76052769514849</v>
+        <v>-26.52407135105824</v>
       </c>
       <c r="F47">
-        <v>0.1322487086094333</v>
+        <v>-2.057509871097156</v>
       </c>
       <c r="G47">
-        <v>-1.483645877400117</v>
+        <v>-8.7598334347862</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.692483512561726</v>
       </c>
       <c r="E48">
-        <v>-16.98247246199461</v>
+        <v>-27.15129670043864</v>
       </c>
       <c r="F48">
-        <v>-0.06132749954636635</v>
+        <v>-1.727355759037385</v>
       </c>
       <c r="G48">
-        <v>-1.776452245700285</v>
+        <v>-8.762599504560812</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.630413126132802</v>
       </c>
       <c r="E49">
-        <v>-16.62302936610979</v>
+        <v>-27.31651354613448</v>
       </c>
       <c r="F49">
-        <v>0.2004788464758202</v>
+        <v>-2.996905013628685</v>
       </c>
       <c r="G49">
-        <v>-1.423865301808594</v>
+        <v>-8.549897598191368</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.606518548611353</v>
       </c>
       <c r="E50">
-        <v>-15.95812258451157</v>
+        <v>-26.57877531707089</v>
       </c>
       <c r="F50">
-        <v>0.003513787275167751</v>
+        <v>-2.632135084540729</v>
       </c>
       <c r="G50">
-        <v>-1.604027333973025</v>
+        <v>-10.20214358956352</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.6102548559779</v>
       </c>
       <c r="E51">
-        <v>-15.77540771525008</v>
+        <v>-24.41060988930844</v>
       </c>
       <c r="F51">
-        <v>0.001011289351310444</v>
+        <v>-2.820957292171862</v>
       </c>
       <c r="G51">
-        <v>-1.114091736824537</v>
+        <v>-9.4678619853263</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.631285187433059</v>
       </c>
       <c r="E52">
-        <v>-15.69946520614145</v>
+        <v>-24.05152907134423</v>
       </c>
       <c r="F52">
-        <v>0.2430817820017988</v>
+        <v>-2.817092958237802</v>
       </c>
       <c r="G52">
-        <v>-1.066107152739217</v>
+        <v>-8.40298418408879</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.659558943771481</v>
       </c>
       <c r="E53">
-        <v>-13.43926307264711</v>
+        <v>-24.83802990852241</v>
       </c>
       <c r="F53">
-        <v>0.1130073905772064</v>
+        <v>-2.384763868879726</v>
       </c>
       <c r="G53">
-        <v>-1.676292957598235</v>
+        <v>-9.671192722921971</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.68696166790186</v>
       </c>
       <c r="E54">
-        <v>-13.87684498753429</v>
+        <v>-22.48263019443882</v>
       </c>
       <c r="F54">
-        <v>-0.1272804554224574</v>
+        <v>-2.282383456465527</v>
       </c>
       <c r="G54">
-        <v>-1.883685847484498</v>
+        <v>-9.154374077536952</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.709915515650271</v>
       </c>
       <c r="E55">
-        <v>-12.76973724756106</v>
+        <v>-24.11045810360604</v>
       </c>
       <c r="F55">
-        <v>0.2173493770012349</v>
+        <v>-3.02011669662253</v>
       </c>
       <c r="G55">
-        <v>-1.558841631877911</v>
+        <v>-9.001616807837003</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.726550560796231</v>
       </c>
       <c r="E56">
-        <v>-12.82486689013044</v>
+        <v>-22.69955768482825</v>
       </c>
       <c r="F56">
-        <v>-0.1116872674321595</v>
+        <v>-2.778910191173162</v>
       </c>
       <c r="G56">
-        <v>-1.74563501281398</v>
+        <v>-9.99661115230146</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.741257044366463</v>
       </c>
       <c r="E57">
-        <v>-12.40910316301222</v>
+        <v>-22.21350298416297</v>
       </c>
       <c r="F57">
-        <v>0.1155032615618413</v>
+        <v>-2.23085072033737</v>
       </c>
       <c r="G57">
-        <v>-2.540701246439911</v>
+        <v>-9.655098331172894</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.758491658682477</v>
       </c>
       <c r="E58">
-        <v>-11.970909904134</v>
+        <v>-22.80179704249942</v>
       </c>
       <c r="F58">
-        <v>0.06395809992264208</v>
+        <v>-2.719139341224163</v>
       </c>
       <c r="G58">
-        <v>-2.351000703202174</v>
+        <v>-9.972408862078996</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-3.786704290122842</v>
       </c>
       <c r="E59">
-        <v>-11.21486758313141</v>
+        <v>-22.23584194644281</v>
       </c>
       <c r="F59">
-        <v>0.264085865867183</v>
+        <v>-2.875393456046831</v>
       </c>
       <c r="G59">
-        <v>-2.737230011742852</v>
+        <v>-10.56564715758348</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-3.832718182590739</v>
       </c>
       <c r="E60">
-        <v>-11.05505320692672</v>
+        <v>-22.29710767129258</v>
       </c>
       <c r="F60">
-        <v>0.2004639358625698</v>
+        <v>-2.178067977798388</v>
       </c>
       <c r="G60">
-        <v>-3.366492838748481</v>
+        <v>-11.37251922638029</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-3.905759914949069</v>
       </c>
       <c r="E61">
-        <v>-10.64501347095419</v>
+        <v>-20.52078657093983</v>
       </c>
       <c r="F61">
-        <v>0.2321357351412061</v>
+        <v>-2.459452787385741</v>
       </c>
       <c r="G61">
-        <v>-3.106367437180382</v>
+        <v>-11.51968857576451</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.010414591142951</v>
       </c>
       <c r="E62">
-        <v>-10.55902680649654</v>
+        <v>-21.39889843729319</v>
       </c>
       <c r="F62">
-        <v>0.1697099676662354</v>
+        <v>-1.726423845709236</v>
       </c>
       <c r="G62">
-        <v>-3.253858346277422</v>
+        <v>-11.45033995810564</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.152741333601228</v>
       </c>
       <c r="E63">
-        <v>-10.37751198284709</v>
+        <v>-20.9113085839393</v>
       </c>
       <c r="F63">
-        <v>-0.08727445170425527</v>
+        <v>-2.498374458173678</v>
       </c>
       <c r="G63">
-        <v>-3.304084004687843</v>
+        <v>-10.90591967696258</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.330518171382487</v>
       </c>
       <c r="E64">
-        <v>-10.64366851417391</v>
+        <v>-20.44342212099279</v>
       </c>
       <c r="F64">
-        <v>-0.3582284589555568</v>
+        <v>-2.976491555721497</v>
       </c>
       <c r="G64">
-        <v>-4.033197684968933</v>
+        <v>-11.97612618201262</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-4.544148191566718</v>
       </c>
       <c r="E65">
-        <v>-10.08127279868732</v>
+        <v>-18.87440097528918</v>
       </c>
       <c r="F65">
-        <v>0.1217358979005048</v>
+        <v>-2.817161712732235</v>
       </c>
       <c r="G65">
-        <v>-3.641882483011117</v>
+        <v>-12.0710650466136</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.784336643306792</v>
       </c>
       <c r="E66">
-        <v>-10.56605046968244</v>
+        <v>-19.74736396669581</v>
       </c>
       <c r="F66">
-        <v>-0.1256609971499844</v>
+        <v>-2.718535461387523</v>
       </c>
       <c r="G66">
-        <v>-3.769374346703341</v>
+        <v>-11.87289567053093</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.045353857015795</v>
       </c>
       <c r="E67">
-        <v>-9.563441795910215</v>
+        <v>-20.77188592619115</v>
       </c>
       <c r="F67">
-        <v>-0.4827635575576288</v>
+        <v>-2.938773502769827</v>
       </c>
       <c r="G67">
-        <v>-3.831491152045189</v>
+        <v>-10.37808925202406</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-5.314235132905994</v>
       </c>
       <c r="E68">
-        <v>-9.917355625031677</v>
+        <v>-21.0141547571275</v>
       </c>
       <c r="F68">
-        <v>-0.2347288196069841</v>
+        <v>-3.012129578124737</v>
       </c>
       <c r="G68">
-        <v>-4.056668262783642</v>
+        <v>-11.39388325995384</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.581030043532207</v>
       </c>
       <c r="E69">
-        <v>-9.498797829450721</v>
+        <v>-19.99413410079579</v>
       </c>
       <c r="F69">
-        <v>-0.4963446411265267</v>
+        <v>-3.054601631601074</v>
       </c>
       <c r="G69">
-        <v>-4.419682928791248</v>
+        <v>-11.78552002162448</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-5.834555959182207</v>
       </c>
       <c r="E70">
-        <v>-9.890067040661455</v>
+        <v>-18.64957582623036</v>
       </c>
       <c r="F70">
-        <v>-0.6783676091154817</v>
+        <v>-3.590689536731607</v>
       </c>
       <c r="G70">
-        <v>-4.155898965184369</v>
+        <v>-12.60157951078774</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-6.065051584773737</v>
       </c>
       <c r="E71">
-        <v>-9.259762328955841</v>
+        <v>-21.26208418057345</v>
       </c>
       <c r="F71">
-        <v>-0.5764370002010025</v>
+        <v>-3.667923199899022</v>
       </c>
       <c r="G71">
-        <v>-4.620611812205405</v>
+        <v>-11.14265325003339</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-6.264701009978123</v>
       </c>
       <c r="E72">
-        <v>-9.336732801664214</v>
+        <v>-21.98351537473541</v>
       </c>
       <c r="F72">
-        <v>-0.8432698796233765</v>
+        <v>-3.988516295395681</v>
       </c>
       <c r="G72">
-        <v>-4.337793482332187</v>
+        <v>-11.17749654177314</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-6.42580198130242</v>
       </c>
       <c r="E73">
-        <v>-9.989566671557988</v>
+        <v>-20.55673359761272</v>
       </c>
       <c r="F73">
-        <v>-0.8542780540391791</v>
+        <v>-3.341999560165348</v>
       </c>
       <c r="G73">
-        <v>-4.817009328645969</v>
+        <v>-11.84491997551511</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-6.545040324708476</v>
       </c>
       <c r="E74">
-        <v>-10.83469766171348</v>
+        <v>-19.16220814084667</v>
       </c>
       <c r="F74">
-        <v>-0.7072370414704473</v>
+        <v>-3.363025181583205</v>
       </c>
       <c r="G74">
-        <v>-4.51209525279145</v>
+        <v>-12.49668213875385</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-6.619265177392287</v>
       </c>
       <c r="E75">
-        <v>-11.34540084640251</v>
+        <v>-20.41630109016086</v>
       </c>
       <c r="F75">
-        <v>-0.9860779347638028</v>
+        <v>-3.097627862869883</v>
       </c>
       <c r="G75">
-        <v>-4.242119624101898</v>
+        <v>-9.648959165635173</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-6.650820815860087</v>
       </c>
       <c r="E76">
-        <v>-11.88472851529403</v>
+        <v>-22.2297013356884</v>
       </c>
       <c r="F76">
-        <v>-0.9424295995754913</v>
+        <v>-3.759247392588056</v>
       </c>
       <c r="G76">
-        <v>-4.152811335696931</v>
+        <v>-10.16766123219531</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-6.641334761268319</v>
       </c>
       <c r="E77">
-        <v>-11.34706732483733</v>
+        <v>-22.53595297587914</v>
       </c>
       <c r="F77">
-        <v>-1.449358972127482</v>
+        <v>-4.528939047145064</v>
       </c>
       <c r="G77">
-        <v>-4.133229005430166</v>
+        <v>-10.59181161829849</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-6.598070017172059</v>
       </c>
       <c r="E78">
-        <v>-12.05494932476835</v>
+        <v>-21.79853173999609</v>
       </c>
       <c r="F78">
-        <v>-1.172912060628217</v>
+        <v>-3.266862494894419</v>
       </c>
       <c r="G78">
-        <v>-3.32549069414166</v>
+        <v>-12.74618622613403</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-6.525699245937322</v>
       </c>
       <c r="E79">
-        <v>-11.90988418840663</v>
+        <v>-23.20063786225098</v>
       </c>
       <c r="F79">
-        <v>-1.25007117072938</v>
+        <v>-3.685011591051373</v>
       </c>
       <c r="G79">
-        <v>-3.078306430404011</v>
+        <v>-12.41125225423215</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-6.433077997575142</v>
       </c>
       <c r="E80">
-        <v>-13.3912612481658</v>
+        <v>-23.56133081696193</v>
       </c>
       <c r="F80">
-        <v>-1.409162443906636</v>
+        <v>-4.022403977476806</v>
       </c>
       <c r="G80">
-        <v>-3.502240255884268</v>
+        <v>-12.51148044798695</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-6.325870131219498</v>
       </c>
       <c r="E81">
-        <v>-13.57150357061909</v>
+        <v>-24.0877025217175</v>
       </c>
       <c r="F81">
-        <v>-1.495483297482762</v>
+        <v>-3.801675542592044</v>
       </c>
       <c r="G81">
-        <v>-3.070930244338379</v>
+        <v>-10.74019830088126</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-6.209146881737138</v>
       </c>
       <c r="E82">
-        <v>-14.57684291421794</v>
+        <v>-24.58168205189621</v>
       </c>
       <c r="F82">
-        <v>-1.464353250485556</v>
+        <v>-4.259755261033545</v>
       </c>
       <c r="G82">
-        <v>-3.118882016208104</v>
+        <v>-9.982544555476121</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-6.086956600971759</v>
       </c>
       <c r="E83">
-        <v>-15.42871680217086</v>
+        <v>-26.7301531461993</v>
       </c>
       <c r="F83">
-        <v>-1.577041866860193</v>
+        <v>-4.67012847238042</v>
       </c>
       <c r="G83">
-        <v>-3.452559280252716</v>
+        <v>-8.344397973144906</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-5.957652754524633</v>
       </c>
       <c r="E84">
-        <v>-16.46031676654018</v>
+        <v>-25.85592218207052</v>
       </c>
       <c r="F84">
-        <v>-1.866724432721388</v>
+        <v>-4.386994150838355</v>
       </c>
       <c r="G84">
-        <v>-2.517194575188049</v>
+        <v>-9.678664064412827</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-5.82206916932028</v>
       </c>
       <c r="E85">
-        <v>-17.96020622804271</v>
+        <v>-26.74688585765764</v>
       </c>
       <c r="F85">
-        <v>-1.971393624269522</v>
+        <v>-3.842301993494943</v>
       </c>
       <c r="G85">
-        <v>-1.696029505278295</v>
+        <v>-8.754921446111712</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-5.673730085803054</v>
       </c>
       <c r="E86">
-        <v>-18.75977171273302</v>
+        <v>-28.84471955560696</v>
       </c>
       <c r="F86">
-        <v>-1.980609211625667</v>
+        <v>-4.382289023990454</v>
       </c>
       <c r="G86">
-        <v>-1.978759242169408</v>
+        <v>-7.757712277094631</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-5.513330428181302</v>
       </c>
       <c r="E87">
-        <v>-19.8807863963838</v>
+        <v>-27.61559661197107</v>
       </c>
       <c r="F87">
-        <v>-1.921634422750759</v>
+        <v>-3.984577408395369</v>
       </c>
       <c r="G87">
-        <v>-2.011171148733603</v>
+        <v>-9.342109169060581</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-5.338195849728566</v>
       </c>
       <c r="E88">
-        <v>-21.4178002878012</v>
+        <v>-29.55360914100469</v>
       </c>
       <c r="F88">
-        <v>-2.213997585527414</v>
+        <v>-4.427092103338268</v>
       </c>
       <c r="G88">
-        <v>-1.929462169460311</v>
+        <v>-8.769145541571906</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-5.151932651675962</v>
       </c>
       <c r="E89">
-        <v>-22.18549890089954</v>
+        <v>-29.41980405526305</v>
       </c>
       <c r="F89">
-        <v>-2.243251380357278</v>
+        <v>-4.521966678715701</v>
       </c>
       <c r="G89">
-        <v>-1.197319921679852</v>
+        <v>-8.08306508204293</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-4.955892571599112</v>
       </c>
       <c r="E90">
-        <v>-23.62226596320914</v>
+        <v>-31.95217426932939</v>
       </c>
       <c r="F90">
-        <v>-2.314046972070135</v>
+        <v>-4.595866163086848</v>
       </c>
       <c r="G90">
-        <v>-1.263439817324223</v>
+        <v>-9.410644043772704</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-4.755727516212936</v>
       </c>
       <c r="E91">
-        <v>-25.91129636223631</v>
+        <v>-32.73596481481398</v>
       </c>
       <c r="F91">
-        <v>-2.46588257516627</v>
+        <v>-4.057311379830777</v>
       </c>
       <c r="G91">
-        <v>-1.594219762731844</v>
+        <v>-8.224137921769698</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-4.556511346095549</v>
       </c>
       <c r="E92">
-        <v>-27.96562953886795</v>
+        <v>-33.12602265922767</v>
       </c>
       <c r="F92">
-        <v>-2.859256030672894</v>
+        <v>-4.479311556043346</v>
       </c>
       <c r="G92">
-        <v>-1.462813401719202</v>
+        <v>-9.478998451299056</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-4.367168751412006</v>
       </c>
       <c r="E93">
-        <v>-30.67350529157557</v>
+        <v>-36.0795749195624</v>
       </c>
       <c r="F93">
-        <v>-2.78825417547674</v>
+        <v>-3.168012584350951</v>
       </c>
       <c r="G93">
-        <v>-1.23987736530585</v>
+        <v>-9.886598355856398</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.196142254215097</v>
       </c>
       <c r="E94">
-        <v>-31.70950240420635</v>
+        <v>-38.62849670612679</v>
       </c>
       <c r="F94">
-        <v>-2.77131406208949</v>
+        <v>-4.670911279576066</v>
       </c>
       <c r="G94">
-        <v>-1.364334099055588</v>
+        <v>-8.960066699229754</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.053009329162947</v>
       </c>
       <c r="E95">
-        <v>-34.75487400352062</v>
+        <v>-38.66690269418584</v>
       </c>
       <c r="F95">
-        <v>-3.06158973901109</v>
+        <v>-4.886282662466924</v>
       </c>
       <c r="G95">
-        <v>-1.295874692439334</v>
+        <v>-9.041585367652599</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.946267958536648</v>
       </c>
       <c r="E96">
-        <v>-36.34469216610447</v>
+        <v>-41.6728901550554</v>
       </c>
       <c r="F96">
-        <v>-2.929680513789297</v>
+        <v>-5.032038048826511</v>
       </c>
       <c r="G96">
-        <v>-2.115983209006946</v>
+        <v>-8.662774901057826</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.878120107441507</v>
       </c>
       <c r="E97">
-        <v>-38.61492939799981</v>
+        <v>-44.84052375986575</v>
       </c>
       <c r="F97">
-        <v>-3.290710364053614</v>
+        <v>-5.436064309133136</v>
       </c>
       <c r="G97">
-        <v>-2.05456530385726</v>
+        <v>-9.982301745080722</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.853148783787018</v>
       </c>
       <c r="E98">
-        <v>-40.98487457059603</v>
+        <v>-45.43124508027032</v>
       </c>
       <c r="F98">
-        <v>-3.166831332434559</v>
+        <v>-5.33237424785511</v>
       </c>
       <c r="G98">
-        <v>-2.271116083115932</v>
+        <v>-9.737220744362677</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-3.86267106705059</v>
       </c>
       <c r="E99">
-        <v>-43.89711809103281</v>
+        <v>-46.84055147619742</v>
       </c>
       <c r="F99">
-        <v>-3.244689584623684</v>
+        <v>-5.4747275292914</v>
       </c>
       <c r="G99">
-        <v>-2.504965462435998</v>
+        <v>-10.14228754587613</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.907866911959314</v>
       </c>
       <c r="E100">
-        <v>-45.14599876676417</v>
+        <v>-49.18389186399858</v>
       </c>
       <c r="F100">
-        <v>-3.08225833407834</v>
+        <v>-5.027691605064022</v>
       </c>
       <c r="G100">
-        <v>-2.957140761878396</v>
+        <v>-8.918178624801884</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.967113218677632</v>
       </c>
       <c r="E101">
-        <v>-47.65663909830471</v>
+        <v>-49.96106630895796</v>
       </c>
       <c r="F101">
-        <v>-3.452748140082628</v>
+        <v>-6.050060996864365</v>
       </c>
       <c r="G101">
-        <v>-3.215244930965877</v>
+        <v>-9.519652786420576</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.043669549313353</v>
       </c>
       <c r="E102">
-        <v>-50.24227888424178</v>
+        <v>-53.19069132657782</v>
       </c>
       <c r="F102">
-        <v>-3.203911542486073</v>
+        <v>-5.49572747131977</v>
       </c>
       <c r="G102">
-        <v>-3.58436923151717</v>
+        <v>-10.43065442140637</v>
       </c>
     </row>
   </sheetData>
